--- a/Documents/TableXlsx/Units.xlsx
+++ b/Documents/TableXlsx/Units.xlsx
@@ -142,11 +142,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -281,9 +281,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.5"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="11.64"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.41"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="101.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="23.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="23.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="20.16"/>
   </cols>
   <sheetData>
